--- a/www/flightdata/xlsx/eoss-359.xlsx
+++ b/www/flightdata/xlsx/eoss-359.xlsx
@@ -3978,7 +3978,7 @@
         <v>31062.47</v>
       </c>
       <c r="I2">
-        <v>807</v>
+        <v>526</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
